--- a/InputData/trans/SoCDTtiNTY/Share of Cargo Dist Transported that is New This Year.xlsx
+++ b/InputData/trans/SoCDTtiNTY/Share of Cargo Dist Transported that is New This Year.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\trans\SoCDTtiNTY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-southkorea\InputData\trans\SoCDTtiNTY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B539881-35F2-4ACF-93AE-EB11A251A4DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9A151A6-74C5-441B-BC57-4DCA391766A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="SoCDTtiNTY-psgr" sheetId="2" r:id="rId2"/>
-    <sheet name="SoCDTtiNTY-frgt" sheetId="4" r:id="rId3"/>
+    <sheet name="AVL" sheetId="5" r:id="rId2"/>
+    <sheet name="SoCDTtiNTY-psgr" sheetId="2" r:id="rId3"/>
+    <sheet name="SoCDTtiNTY-frgt" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1" iterateDelta="1.0000000000000001E-5"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -26,6 +27,7 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -33,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="30">
   <si>
     <t>SoCDTtiNTY Share of Cargo Dist Transported that is New This Year</t>
   </si>
@@ -111,12 +113,27 @@
   </si>
   <si>
     <t>hydrogen vehicle</t>
+  </si>
+  <si>
+    <t>Vehicle Lifetime (years)</t>
+  </si>
+  <si>
+    <t>Passenger</t>
+  </si>
+  <si>
+    <t>Freight</t>
+  </si>
+  <si>
+    <t>Calculated SoCDTtiNTY values</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -154,7 +171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -166,6 +183,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -184,9 +206,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -224,9 +246,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -259,9 +281,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -294,9 +333,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -537,6 +593,187 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DE974D0-35AB-448C-ABAC-291E7575B7A2}">
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="6">
+        <v>11.42095169122128</v>
+      </c>
+      <c r="C2" s="6">
+        <v>11.42095169122128</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="6">
+        <v>13.396516093228287</v>
+      </c>
+      <c r="C3" s="6">
+        <v>13.396516093228287</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="6">
+        <v>24</v>
+      </c>
+      <c r="C4" s="6">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5">
+        <v>34</v>
+      </c>
+      <c r="C5">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6">
+        <v>33</v>
+      </c>
+      <c r="C6">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7">
+        <v>17</v>
+      </c>
+      <c r="C7">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="7">
+        <f>1/B2</f>
+        <v>8.7558377535967555E-2</v>
+      </c>
+      <c r="C11" s="7">
+        <f>1/C2</f>
+        <v>8.7558377535967555E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="7">
+        <f t="shared" ref="B12:C16" si="0">1/B3</f>
+        <v>7.4646273183330336E-2</v>
+      </c>
+      <c r="C12" s="7">
+        <f t="shared" si="0"/>
+        <v>7.4646273183330336E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="7">
+        <f t="shared" si="0"/>
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="C13" s="7">
+        <f t="shared" si="0"/>
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="7">
+        <f t="shared" si="0"/>
+        <v>2.9411764705882353E-2</v>
+      </c>
+      <c r="C14" s="7">
+        <f t="shared" si="0"/>
+        <v>2.9411764705882353E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="7">
+        <f t="shared" si="0"/>
+        <v>3.0303030303030304E-2</v>
+      </c>
+      <c r="C15" s="7">
+        <f t="shared" si="0"/>
+        <v>3.0303030303030304E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="C16" s="7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
@@ -579,32 +816,32 @@
         <v>12</v>
       </c>
       <c r="B2">
-        <f>1/17</f>
-        <v>5.8823529411764705E-2</v>
+        <f>AVL!$B$11</f>
+        <v>8.7558377535967555E-2</v>
       </c>
       <c r="C2">
-        <f t="shared" ref="C2:H2" si="0">1/17</f>
-        <v>5.8823529411764705E-2</v>
+        <f>AVL!$B$11</f>
+        <v>8.7558377535967555E-2</v>
       </c>
       <c r="D2">
-        <f t="shared" si="0"/>
-        <v>5.8823529411764705E-2</v>
+        <f>AVL!$B$11</f>
+        <v>8.7558377535967555E-2</v>
       </c>
       <c r="E2">
-        <f t="shared" si="0"/>
-        <v>5.8823529411764705E-2</v>
+        <f>AVL!$B$11</f>
+        <v>8.7558377535967555E-2</v>
       </c>
       <c r="F2">
-        <f t="shared" si="0"/>
-        <v>5.8823529411764705E-2</v>
+        <f>AVL!$B$11</f>
+        <v>8.7558377535967555E-2</v>
       </c>
       <c r="G2">
-        <f t="shared" si="0"/>
-        <v>5.8823529411764705E-2</v>
+        <f>AVL!$B$11</f>
+        <v>8.7558377535967555E-2</v>
       </c>
       <c r="H2">
-        <f t="shared" si="0"/>
-        <v>5.8823529411764705E-2</v>
+        <f>AVL!$B$11</f>
+        <v>8.7558377535967555E-2</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -612,25 +849,32 @@
         <v>13</v>
       </c>
       <c r="B3">
-        <v>0.09</v>
+        <f>AVL!$B$12</f>
+        <v>7.4646273183330336E-2</v>
       </c>
       <c r="C3">
-        <v>0.09</v>
+        <f>AVL!$B$12</f>
+        <v>7.4646273183330336E-2</v>
       </c>
       <c r="D3">
-        <v>0.09</v>
+        <f>AVL!$B$12</f>
+        <v>7.4646273183330336E-2</v>
       </c>
       <c r="E3">
-        <v>0.09</v>
+        <f>AVL!$B$12</f>
+        <v>7.4646273183330336E-2</v>
       </c>
       <c r="F3">
-        <v>0.09</v>
+        <f>AVL!$B$12</f>
+        <v>7.4646273183330336E-2</v>
       </c>
       <c r="G3">
-        <v>0.09</v>
+        <f>AVL!$B$12</f>
+        <v>7.4646273183330336E-2</v>
       </c>
       <c r="H3">
-        <v>0.09</v>
+        <f>AVL!$B$12</f>
+        <v>7.4646273183330336E-2</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -638,25 +882,32 @@
         <v>14</v>
       </c>
       <c r="B4">
-        <v>4.1599999999999998E-2</v>
+        <f>AVL!$B$13</f>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="C4">
-        <v>4.1599999999999998E-2</v>
+        <f>AVL!$B$13</f>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="D4">
-        <v>4.1599999999999998E-2</v>
+        <f>AVL!$B$13</f>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="E4">
-        <v>4.1599999999999998E-2</v>
+        <f>AVL!$B$13</f>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="F4">
-        <v>4.1599999999999998E-2</v>
+        <f>AVL!$B$13</f>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="G4">
-        <v>4.1599999999999998E-2</v>
+        <f>AVL!$B$13</f>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="H4">
-        <v>4.1599999999999998E-2</v>
+        <f>AVL!$B$13</f>
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -664,25 +915,32 @@
         <v>15</v>
       </c>
       <c r="B5">
-        <v>2.9000000000000001E-2</v>
+        <f>AVL!$B$14</f>
+        <v>2.9411764705882353E-2</v>
       </c>
       <c r="C5">
-        <v>2.9000000000000001E-2</v>
+        <f>AVL!$B$14</f>
+        <v>2.9411764705882353E-2</v>
       </c>
       <c r="D5">
-        <v>2.9000000000000001E-2</v>
+        <f>AVL!$B$14</f>
+        <v>2.9411764705882353E-2</v>
       </c>
       <c r="E5">
-        <v>2.9000000000000001E-2</v>
+        <f>AVL!$B$14</f>
+        <v>2.9411764705882353E-2</v>
       </c>
       <c r="F5">
-        <v>2.9000000000000001E-2</v>
+        <f>AVL!$B$14</f>
+        <v>2.9411764705882353E-2</v>
       </c>
       <c r="G5">
-        <v>2.9000000000000001E-2</v>
+        <f>AVL!$B$14</f>
+        <v>2.9411764705882353E-2</v>
       </c>
       <c r="H5">
-        <v>2.9000000000000001E-2</v>
+        <f>AVL!$B$14</f>
+        <v>2.9411764705882353E-2</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -690,25 +948,32 @@
         <v>16</v>
       </c>
       <c r="B6">
-        <v>2.9819999999999999E-2</v>
+        <f>AVL!$B$15</f>
+        <v>3.0303030303030304E-2</v>
       </c>
       <c r="C6">
-        <v>2.9819999999999999E-2</v>
+        <f>AVL!$B$15</f>
+        <v>3.0303030303030304E-2</v>
       </c>
       <c r="D6">
-        <v>2.9819999999999999E-2</v>
+        <f>AVL!$B$15</f>
+        <v>3.0303030303030304E-2</v>
       </c>
       <c r="E6">
-        <v>2.9819999999999999E-2</v>
+        <f>AVL!$B$15</f>
+        <v>3.0303030303030304E-2</v>
       </c>
       <c r="F6">
-        <v>2.9819999999999999E-2</v>
+        <f>AVL!$B$15</f>
+        <v>3.0303030303030304E-2</v>
       </c>
       <c r="G6">
-        <v>2.9819999999999999E-2</v>
+        <f>AVL!$B$15</f>
+        <v>3.0303030303030304E-2</v>
       </c>
       <c r="H6">
-        <v>2.9819999999999999E-2</v>
+        <f>AVL!$B$15</f>
+        <v>3.0303030303030304E-2</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -716,25 +981,32 @@
         <v>17</v>
       </c>
       <c r="B7">
-        <v>5.8500000000000003E-2</v>
+        <f>AVL!$B$16</f>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="C7">
-        <v>5.8500000000000003E-2</v>
+        <f>AVL!$B$16</f>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="D7">
-        <v>5.8500000000000003E-2</v>
+        <f>AVL!$B$16</f>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="E7">
-        <v>5.8500000000000003E-2</v>
+        <f>AVL!$B$16</f>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="F7">
-        <v>5.8500000000000003E-2</v>
+        <f>AVL!$B$16</f>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="G7">
-        <v>5.8500000000000003E-2</v>
+        <f>AVL!$B$16</f>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="H7">
-        <v>5.8500000000000003E-2</v>
+        <f>AVL!$B$16</f>
+        <v>5.8823529411764705E-2</v>
       </c>
     </row>
   </sheetData>
@@ -742,7 +1014,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
@@ -785,32 +1057,32 @@
         <v>12</v>
       </c>
       <c r="B2">
-        <f>1/17</f>
-        <v>5.8823529411764705E-2</v>
+        <f>AVL!$C$11</f>
+        <v>8.7558377535967555E-2</v>
       </c>
       <c r="C2">
-        <f t="shared" ref="C2:H2" si="0">1/17</f>
-        <v>5.8823529411764705E-2</v>
+        <f>AVL!$C$11</f>
+        <v>8.7558377535967555E-2</v>
       </c>
       <c r="D2">
-        <f t="shared" si="0"/>
-        <v>5.8823529411764705E-2</v>
+        <f>AVL!$C$11</f>
+        <v>8.7558377535967555E-2</v>
       </c>
       <c r="E2">
-        <f t="shared" si="0"/>
-        <v>5.8823529411764705E-2</v>
+        <f>AVL!$C$11</f>
+        <v>8.7558377535967555E-2</v>
       </c>
       <c r="F2">
-        <f t="shared" si="0"/>
-        <v>5.8823529411764705E-2</v>
+        <f>AVL!$C$11</f>
+        <v>8.7558377535967555E-2</v>
       </c>
       <c r="G2">
-        <f t="shared" si="0"/>
-        <v>5.8823529411764705E-2</v>
+        <f>AVL!$C$11</f>
+        <v>8.7558377535967555E-2</v>
       </c>
       <c r="H2">
-        <f t="shared" si="0"/>
-        <v>5.8823529411764705E-2</v>
+        <f>AVL!$C$11</f>
+        <v>8.7558377535967555E-2</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -818,32 +1090,32 @@
         <v>13</v>
       </c>
       <c r="B3">
-        <f>1/19</f>
-        <v>5.2631578947368418E-2</v>
+        <f>AVL!$C$12</f>
+        <v>7.4646273183330336E-2</v>
       </c>
       <c r="C3">
-        <f t="shared" ref="C3:H3" si="1">1/19</f>
-        <v>5.2631578947368418E-2</v>
+        <f>AVL!$C$12</f>
+        <v>7.4646273183330336E-2</v>
       </c>
       <c r="D3">
-        <f t="shared" si="1"/>
-        <v>5.2631578947368418E-2</v>
+        <f>AVL!$C$12</f>
+        <v>7.4646273183330336E-2</v>
       </c>
       <c r="E3">
-        <f t="shared" si="1"/>
-        <v>5.2631578947368418E-2</v>
+        <f>AVL!$C$12</f>
+        <v>7.4646273183330336E-2</v>
       </c>
       <c r="F3">
-        <f t="shared" si="1"/>
-        <v>5.2631578947368418E-2</v>
+        <f>AVL!$C$12</f>
+        <v>7.4646273183330336E-2</v>
       </c>
       <c r="G3">
-        <f t="shared" si="1"/>
-        <v>5.2631578947368418E-2</v>
+        <f>AVL!$C$12</f>
+        <v>7.4646273183330336E-2</v>
       </c>
       <c r="H3">
-        <f t="shared" si="1"/>
-        <v>5.2631578947368418E-2</v>
+        <f>AVL!$C$12</f>
+        <v>7.4646273183330336E-2</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -851,25 +1123,32 @@
         <v>14</v>
       </c>
       <c r="B4">
-        <v>2.8000000000000001E-2</v>
+        <f>AVL!$C$13</f>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="C4">
-        <v>2.8000000000000001E-2</v>
+        <f>AVL!$C$13</f>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="D4">
-        <v>2.8000000000000001E-2</v>
+        <f>AVL!$C$13</f>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="E4">
-        <v>2.8000000000000001E-2</v>
+        <f>AVL!$C$13</f>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="F4">
-        <v>2.8000000000000001E-2</v>
+        <f>AVL!$C$13</f>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="G4">
-        <v>2.8000000000000001E-2</v>
+        <f>AVL!$C$13</f>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="H4">
-        <v>2.8000000000000001E-2</v>
+        <f>AVL!$C$13</f>
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -877,25 +1156,32 @@
         <v>15</v>
       </c>
       <c r="B5">
-        <v>2.9000000000000001E-2</v>
+        <f>AVL!$C$14</f>
+        <v>2.9411764705882353E-2</v>
       </c>
       <c r="C5">
-        <v>2.9000000000000001E-2</v>
+        <f>AVL!$C$14</f>
+        <v>2.9411764705882353E-2</v>
       </c>
       <c r="D5">
-        <v>2.9000000000000001E-2</v>
+        <f>AVL!$C$14</f>
+        <v>2.9411764705882353E-2</v>
       </c>
       <c r="E5">
-        <v>2.9000000000000001E-2</v>
+        <f>AVL!$C$14</f>
+        <v>2.9411764705882353E-2</v>
       </c>
       <c r="F5">
-        <v>2.9000000000000001E-2</v>
+        <f>AVL!$C$14</f>
+        <v>2.9411764705882353E-2</v>
       </c>
       <c r="G5">
-        <v>2.9000000000000001E-2</v>
+        <f>AVL!$C$14</f>
+        <v>2.9411764705882353E-2</v>
       </c>
       <c r="H5">
-        <v>2.9000000000000001E-2</v>
+        <f>AVL!$C$14</f>
+        <v>2.9411764705882353E-2</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -903,25 +1189,32 @@
         <v>16</v>
       </c>
       <c r="B6">
-        <v>3.0300000000000001E-2</v>
+        <f>AVL!$C$15</f>
+        <v>3.0303030303030304E-2</v>
       </c>
       <c r="C6">
-        <v>3.0300000000000001E-2</v>
+        <f>AVL!$C$15</f>
+        <v>3.0303030303030304E-2</v>
       </c>
       <c r="D6">
-        <v>3.0300000000000001E-2</v>
+        <f>AVL!$C$15</f>
+        <v>3.0303030303030304E-2</v>
       </c>
       <c r="E6">
-        <v>3.0300000000000001E-2</v>
+        <f>AVL!$C$15</f>
+        <v>3.0303030303030304E-2</v>
       </c>
       <c r="F6">
-        <v>3.0300000000000001E-2</v>
+        <f>AVL!$C$15</f>
+        <v>3.0303030303030304E-2</v>
       </c>
       <c r="G6">
-        <v>3.0300000000000001E-2</v>
+        <f>AVL!$C$15</f>
+        <v>3.0303030303030304E-2</v>
       </c>
       <c r="H6">
-        <v>3.0300000000000001E-2</v>
+        <f>AVL!$C$15</f>
+        <v>3.0303030303030304E-2</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -929,28 +1222,206 @@
         <v>17</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <f>AVL!$C$16</f>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <f>AVL!$C$16</f>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <f>AVL!$C$16</f>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <f>AVL!$C$16</f>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <f>AVL!$C$16</f>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <f>AVL!$C$16</f>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <f>AVL!$C$16</f>
+        <v>5.8823529411764705E-2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
+    <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="40f4d404-d193-41dc-bb72-733c1e774208" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1149AAAE-ABCC-460E-97F6-A6D332D4802A}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{441C2D10-A603-4499-828F-5FADDAF9DE77}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30A502D4-C09A-449A-A258-EE541B816382}"/>
 </file>
--- a/InputData/trans/SoCDTtiNTY/Share of Cargo Dist Transported that is New This Year.xlsx
+++ b/InputData/trans/SoCDTtiNTY/Share of Cargo Dist Transported that is New This Year.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-southkorea\InputData\trans\SoCDTtiNTY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Desktop\EPS Models\SouthKorea EPS\InputData\trans\SoCDTtiNTY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9A151A6-74C5-441B-BC57-4DCA391766A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91EF0957-B562-4E54-8945-54421D16958F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43725" yWindow="3000" windowWidth="20145" windowHeight="11235" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,9 @@
     <sheet name="SoCDTtiNTY-psgr" sheetId="2" r:id="rId3"/>
     <sheet name="SoCDTtiNTY-frgt" sheetId="4" r:id="rId4"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId5"/>
+  </externalReferences>
   <calcPr calcId="191029" iterate="1" iterateDelta="1.0000000000000001E-5"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -134,7 +137,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -146,6 +149,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -171,7 +181,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -188,6 +198,7 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -205,10 +216,66 @@
 </styleSheet>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="About"/>
+      <sheetName val="NTS 1-20"/>
+      <sheetName val="Data"/>
+      <sheetName val="SK calcs"/>
+      <sheetName val="AVL"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2">
+        <row r="16">
+          <cell r="A16">
+            <v>24</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="C22">
+            <v>34</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="C28">
+            <v>33</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="A48">
+            <v>17.22332068760786</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3">
+        <row r="36">
+          <cell r="J36">
+            <v>15.4</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="J37">
+            <v>16.8</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="4" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -246,9 +313,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -281,26 +348,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -333,26 +383,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -527,14 +560,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -542,47 +575,47 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -595,9 +628,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DE974D0-35AB-448C-ABAC-291E7575B7A2}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>26</v>
       </c>
@@ -608,78 +641,90 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="6">
-        <v>11.42095169122128</v>
-      </c>
-      <c r="C2" s="6">
-        <v>11.42095169122128</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B2" s="8">
+        <f>'[1]SK calcs'!J36</f>
+        <v>15.4</v>
+      </c>
+      <c r="C2" s="8">
+        <f t="shared" ref="C2:C7" si="0">B2</f>
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="6">
-        <v>13.396516093228287</v>
-      </c>
-      <c r="C3" s="6">
-        <v>13.396516093228287</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B3" s="8">
+        <f>'[1]SK calcs'!J37</f>
+        <v>16.8</v>
+      </c>
+      <c r="C3" s="8">
+        <f t="shared" si="0"/>
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="6">
+        <f>ROUND([1]Data!A16,0)</f>
         <v>24</v>
       </c>
       <c r="C4" s="6">
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
       <c r="B5">
+        <f>ROUND([1]Data!C22,0)</f>
         <v>34</v>
       </c>
       <c r="C5">
+        <f t="shared" si="0"/>
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>16</v>
       </c>
       <c r="B6">
+        <f>ROUND([1]Data!C28,0)</f>
         <v>33</v>
       </c>
       <c r="C6">
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>17</v>
       </c>
       <c r="B7">
+        <f>ROUND([1]Data!A48,0)</f>
         <v>17</v>
       </c>
       <c r="C7">
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>26</v>
       </c>
@@ -690,81 +735,81 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="7">
         <f>1/B2</f>
-        <v>8.7558377535967555E-2</v>
+        <v>6.4935064935064929E-2</v>
       </c>
       <c r="C11" s="7">
         <f>1/C2</f>
-        <v>8.7558377535967555E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>6.4935064935064929E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="7">
-        <f t="shared" ref="B12:C16" si="0">1/B3</f>
-        <v>7.4646273183330336E-2</v>
+        <f t="shared" ref="B12:C16" si="1">1/B3</f>
+        <v>5.9523809523809521E-2</v>
       </c>
       <c r="C12" s="7">
-        <f t="shared" si="0"/>
-        <v>7.4646273183330336E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>5.9523809523809521E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4.1666666666666664E-2</v>
       </c>
       <c r="C13" s="7">
-        <f t="shared" si="0"/>
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>15</v>
       </c>
       <c r="B14" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.9411764705882353E-2</v>
       </c>
       <c r="C14" s="7">
-        <f t="shared" si="0"/>
-        <v>2.9411764705882353E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>2.9411764705882353E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>16</v>
       </c>
       <c r="B15" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.0303030303030304E-2</v>
       </c>
       <c r="C15" s="7">
-        <f t="shared" si="0"/>
-        <v>3.0303030303030304E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>3.0303030303030304E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>17</v>
       </c>
       <c r="B16" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5.8823529411764705E-2</v>
       </c>
       <c r="C16" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5.8823529411764705E-2</v>
       </c>
     </row>
@@ -779,13 +824,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.140625" customWidth="1"/>
-    <col min="2" max="8" width="14.42578125" customWidth="1"/>
+    <col min="1" max="1" width="19.109375" customWidth="1"/>
+    <col min="2" max="8" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>18</v>
       </c>
@@ -811,73 +856,73 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
       <c r="B2">
         <f>AVL!$B$11</f>
-        <v>8.7558377535967555E-2</v>
+        <v>6.4935064935064929E-2</v>
       </c>
       <c r="C2">
         <f>AVL!$B$11</f>
-        <v>8.7558377535967555E-2</v>
+        <v>6.4935064935064929E-2</v>
       </c>
       <c r="D2">
         <f>AVL!$B$11</f>
-        <v>8.7558377535967555E-2</v>
+        <v>6.4935064935064929E-2</v>
       </c>
       <c r="E2">
         <f>AVL!$B$11</f>
-        <v>8.7558377535967555E-2</v>
+        <v>6.4935064935064929E-2</v>
       </c>
       <c r="F2">
         <f>AVL!$B$11</f>
-        <v>8.7558377535967555E-2</v>
+        <v>6.4935064935064929E-2</v>
       </c>
       <c r="G2">
         <f>AVL!$B$11</f>
-        <v>8.7558377535967555E-2</v>
+        <v>6.4935064935064929E-2</v>
       </c>
       <c r="H2">
         <f>AVL!$B$11</f>
-        <v>8.7558377535967555E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <v>6.4935064935064929E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
       <c r="B3">
         <f>AVL!$B$12</f>
-        <v>7.4646273183330336E-2</v>
+        <v>5.9523809523809521E-2</v>
       </c>
       <c r="C3">
         <f>AVL!$B$12</f>
-        <v>7.4646273183330336E-2</v>
+        <v>5.9523809523809521E-2</v>
       </c>
       <c r="D3">
         <f>AVL!$B$12</f>
-        <v>7.4646273183330336E-2</v>
+        <v>5.9523809523809521E-2</v>
       </c>
       <c r="E3">
         <f>AVL!$B$12</f>
-        <v>7.4646273183330336E-2</v>
+        <v>5.9523809523809521E-2</v>
       </c>
       <c r="F3">
         <f>AVL!$B$12</f>
-        <v>7.4646273183330336E-2</v>
+        <v>5.9523809523809521E-2</v>
       </c>
       <c r="G3">
         <f>AVL!$B$12</f>
-        <v>7.4646273183330336E-2</v>
+        <v>5.9523809523809521E-2</v>
       </c>
       <c r="H3">
         <f>AVL!$B$12</f>
-        <v>7.4646273183330336E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <v>5.9523809523809521E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -910,7 +955,7 @@
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -943,7 +988,7 @@
         <v>2.9411764705882353E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -976,7 +1021,7 @@
         <v>3.0303030303030304E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -1020,13 +1065,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.140625" customWidth="1"/>
-    <col min="2" max="8" width="14.42578125" customWidth="1"/>
+    <col min="1" max="1" width="19.109375" customWidth="1"/>
+    <col min="2" max="8" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>18</v>
       </c>
@@ -1052,73 +1097,73 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
       <c r="B2">
         <f>AVL!$C$11</f>
-        <v>8.7558377535967555E-2</v>
+        <v>6.4935064935064929E-2</v>
       </c>
       <c r="C2">
         <f>AVL!$C$11</f>
-        <v>8.7558377535967555E-2</v>
+        <v>6.4935064935064929E-2</v>
       </c>
       <c r="D2">
         <f>AVL!$C$11</f>
-        <v>8.7558377535967555E-2</v>
+        <v>6.4935064935064929E-2</v>
       </c>
       <c r="E2">
         <f>AVL!$C$11</f>
-        <v>8.7558377535967555E-2</v>
+        <v>6.4935064935064929E-2</v>
       </c>
       <c r="F2">
         <f>AVL!$C$11</f>
-        <v>8.7558377535967555E-2</v>
+        <v>6.4935064935064929E-2</v>
       </c>
       <c r="G2">
         <f>AVL!$C$11</f>
-        <v>8.7558377535967555E-2</v>
+        <v>6.4935064935064929E-2</v>
       </c>
       <c r="H2">
         <f>AVL!$C$11</f>
-        <v>8.7558377535967555E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <v>6.4935064935064929E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
       <c r="B3">
         <f>AVL!$C$12</f>
-        <v>7.4646273183330336E-2</v>
+        <v>5.9523809523809521E-2</v>
       </c>
       <c r="C3">
         <f>AVL!$C$12</f>
-        <v>7.4646273183330336E-2</v>
+        <v>5.9523809523809521E-2</v>
       </c>
       <c r="D3">
         <f>AVL!$C$12</f>
-        <v>7.4646273183330336E-2</v>
+        <v>5.9523809523809521E-2</v>
       </c>
       <c r="E3">
         <f>AVL!$C$12</f>
-        <v>7.4646273183330336E-2</v>
+        <v>5.9523809523809521E-2</v>
       </c>
       <c r="F3">
         <f>AVL!$C$12</f>
-        <v>7.4646273183330336E-2</v>
+        <v>5.9523809523809521E-2</v>
       </c>
       <c r="G3">
         <f>AVL!$C$12</f>
-        <v>7.4646273183330336E-2</v>
+        <v>5.9523809523809521E-2</v>
       </c>
       <c r="H3">
         <f>AVL!$C$12</f>
-        <v>7.4646273183330336E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <v>5.9523809523809521E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1151,7 +1196,7 @@
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -1184,7 +1229,7 @@
         <v>2.9411764705882353E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1217,7 +1262,7 @@
         <v>3.0303030303030304E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -1256,6 +1301,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
     <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
@@ -1399,29 +1459,37 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1149AAAE-ABCC-460E-97F6-A6D332D4802A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30A502D4-C09A-449A-A258-EE541B816382}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{441C2D10-A603-4499-828F-5FADDAF9DE77}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{441C2D10-A603-4499-828F-5FADDAF9DE77}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30A502D4-C09A-449A-A258-EE541B816382}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1149AAAE-ABCC-460E-97F6-A6D332D4802A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/InputData/trans/SoCDTtiNTY/Share of Cargo Dist Transported that is New This Year.xlsx
+++ b/InputData/trans/SoCDTtiNTY/Share of Cargo Dist Transported that is New This Year.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Desktop\EPS Models\SouthKorea EPS\InputData\trans\SoCDTtiNTY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-southkorea-ci\InputData\trans\SoCDTtiNTY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91EF0957-B562-4E54-8945-54421D16958F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D1A8964-98DB-4AA4-BED4-2CA2BD5126D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43725" yWindow="3000" windowWidth="20145" windowHeight="11235" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38505" yWindow="-4650" windowWidth="19410" windowHeight="20985" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -18,10 +18,7 @@
     <sheet name="SoCDTtiNTY-psgr" sheetId="2" r:id="rId3"/>
     <sheet name="SoCDTtiNTY-frgt" sheetId="4" r:id="rId4"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId5"/>
-  </externalReferences>
-  <calcPr calcId="191029" iterate="1" iterateDelta="1.0000000000000001E-5"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -137,7 +134,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -158,6 +155,13 @@
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -214,62 +218,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="About"/>
-      <sheetName val="NTS 1-20"/>
-      <sheetName val="Data"/>
-      <sheetName val="SK calcs"/>
-      <sheetName val="AVL"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2">
-        <row r="16">
-          <cell r="A16">
-            <v>24</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="C22">
-            <v>34</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="C28">
-            <v>33</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="A48">
-            <v>17.22332068760786</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="3">
-        <row r="36">
-          <cell r="J36">
-            <v>15.4</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="J37">
-            <v>16.8</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="4" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -560,14 +508,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -575,52 +523,53 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2">
       <c r="B4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2">
       <c r="B5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>11</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -628,9 +577,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DE974D0-35AB-448C-ABAC-291E7575B7A2}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="43.5">
       <c r="A1" s="2" t="s">
         <v>26</v>
       </c>
@@ -641,90 +590,78 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
       <c r="B2" s="8">
-        <f>'[1]SK calcs'!J36</f>
-        <v>15.4</v>
+        <v>15.6</v>
       </c>
       <c r="C2" s="8">
-        <f t="shared" ref="C2:C7" si="0">B2</f>
-        <v>15.4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>17.75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="8">
-        <f>'[1]SK calcs'!J37</f>
-        <v>16.8</v>
+        <v>15.5</v>
       </c>
       <c r="C3" s="8">
-        <f t="shared" si="0"/>
-        <v>16.8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>17.75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="6">
-        <f>ROUND([1]Data!A16,0)</f>
         <v>24</v>
       </c>
       <c r="C4" s="6">
-        <f t="shared" si="0"/>
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
       <c r="B5">
-        <f>ROUND([1]Data!C22,0)</f>
         <v>34</v>
       </c>
       <c r="C5">
-        <f t="shared" si="0"/>
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>16</v>
       </c>
       <c r="B6">
-        <f>ROUND([1]Data!C28,0)</f>
         <v>33</v>
       </c>
       <c r="C6">
-        <f t="shared" si="0"/>
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>17</v>
       </c>
       <c r="B7">
-        <f>ROUND([1]Data!A48,0)</f>
         <v>17</v>
       </c>
       <c r="C7">
-        <f t="shared" si="0"/>
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="43.5">
       <c r="A10" s="2" t="s">
         <v>26</v>
       </c>
@@ -735,85 +672,86 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="7">
         <f>1/B2</f>
-        <v>6.4935064935064929E-2</v>
+        <v>6.4102564102564111E-2</v>
       </c>
       <c r="C11" s="7">
         <f>1/C2</f>
-        <v>6.4935064935064929E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+        <v>5.6338028169014086E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="7">
-        <f t="shared" ref="B12:C16" si="1">1/B3</f>
-        <v>5.9523809523809521E-2</v>
+        <f t="shared" ref="B12:C16" si="0">1/B3</f>
+        <v>6.4516129032258063E-2</v>
       </c>
       <c r="C12" s="7">
-        <f t="shared" si="1"/>
-        <v>5.9523809523809521E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>5.6338028169014086E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>4.1666666666666664E-2</v>
       </c>
       <c r="C13" s="7">
-        <f t="shared" si="1"/>
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>15</v>
       </c>
       <c r="B14" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2.9411764705882353E-2</v>
       </c>
       <c r="C14" s="7">
-        <f t="shared" si="1"/>
-        <v>2.9411764705882353E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>2.9411764705882353E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>16</v>
       </c>
       <c r="B15" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3.0303030303030304E-2</v>
       </c>
       <c r="C15" s="7">
-        <f t="shared" si="1"/>
-        <v>3.0303030303030304E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>3.0303030303030304E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>17</v>
       </c>
       <c r="B16" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>5.8823529411764705E-2</v>
       </c>
       <c r="C16" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>5.8823529411764705E-2</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -824,13 +762,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="19.109375" customWidth="1"/>
-    <col min="2" max="8" width="14.44140625" customWidth="1"/>
+    <col min="1" max="1" width="19.08984375" customWidth="1"/>
+    <col min="2" max="8" width="14.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" s="4" customFormat="1" ht="29">
       <c r="A1" s="2" t="s">
         <v>18</v>
       </c>
@@ -856,73 +794,73 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>12</v>
       </c>
       <c r="B2">
         <f>AVL!$B$11</f>
-        <v>6.4935064935064929E-2</v>
+        <v>6.4102564102564111E-2</v>
       </c>
       <c r="C2">
         <f>AVL!$B$11</f>
-        <v>6.4935064935064929E-2</v>
+        <v>6.4102564102564111E-2</v>
       </c>
       <c r="D2">
         <f>AVL!$B$11</f>
-        <v>6.4935064935064929E-2</v>
+        <v>6.4102564102564111E-2</v>
       </c>
       <c r="E2">
         <f>AVL!$B$11</f>
-        <v>6.4935064935064929E-2</v>
+        <v>6.4102564102564111E-2</v>
       </c>
       <c r="F2">
         <f>AVL!$B$11</f>
-        <v>6.4935064935064929E-2</v>
+        <v>6.4102564102564111E-2</v>
       </c>
       <c r="G2">
         <f>AVL!$B$11</f>
-        <v>6.4935064935064929E-2</v>
+        <v>6.4102564102564111E-2</v>
       </c>
       <c r="H2">
         <f>AVL!$B$11</f>
-        <v>6.4935064935064929E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>6.4102564102564111E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>13</v>
       </c>
       <c r="B3">
         <f>AVL!$B$12</f>
-        <v>5.9523809523809521E-2</v>
+        <v>6.4516129032258063E-2</v>
       </c>
       <c r="C3">
         <f>AVL!$B$12</f>
-        <v>5.9523809523809521E-2</v>
+        <v>6.4516129032258063E-2</v>
       </c>
       <c r="D3">
         <f>AVL!$B$12</f>
-        <v>5.9523809523809521E-2</v>
+        <v>6.4516129032258063E-2</v>
       </c>
       <c r="E3">
         <f>AVL!$B$12</f>
-        <v>5.9523809523809521E-2</v>
+        <v>6.4516129032258063E-2</v>
       </c>
       <c r="F3">
         <f>AVL!$B$12</f>
-        <v>5.9523809523809521E-2</v>
+        <v>6.4516129032258063E-2</v>
       </c>
       <c r="G3">
         <f>AVL!$B$12</f>
-        <v>5.9523809523809521E-2</v>
+        <v>6.4516129032258063E-2</v>
       </c>
       <c r="H3">
         <f>AVL!$B$12</f>
-        <v>5.9523809523809521E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+        <v>6.4516129032258063E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -955,7 +893,7 @@
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -988,7 +926,7 @@
         <v>2.9411764705882353E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1021,7 +959,7 @@
         <v>3.0303030303030304E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -1055,6 +993,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1065,13 +1004,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="19.109375" customWidth="1"/>
-    <col min="2" max="8" width="14.44140625" customWidth="1"/>
+    <col min="1" max="1" width="19.08984375" customWidth="1"/>
+    <col min="2" max="8" width="14.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" s="4" customFormat="1" ht="29">
       <c r="A1" s="2" t="s">
         <v>18</v>
       </c>
@@ -1097,73 +1036,73 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>12</v>
       </c>
       <c r="B2">
         <f>AVL!$C$11</f>
-        <v>6.4935064935064929E-2</v>
+        <v>5.6338028169014086E-2</v>
       </c>
       <c r="C2">
         <f>AVL!$C$11</f>
-        <v>6.4935064935064929E-2</v>
+        <v>5.6338028169014086E-2</v>
       </c>
       <c r="D2">
         <f>AVL!$C$11</f>
-        <v>6.4935064935064929E-2</v>
+        <v>5.6338028169014086E-2</v>
       </c>
       <c r="E2">
         <f>AVL!$C$11</f>
-        <v>6.4935064935064929E-2</v>
+        <v>5.6338028169014086E-2</v>
       </c>
       <c r="F2">
         <f>AVL!$C$11</f>
-        <v>6.4935064935064929E-2</v>
+        <v>5.6338028169014086E-2</v>
       </c>
       <c r="G2">
         <f>AVL!$C$11</f>
-        <v>6.4935064935064929E-2</v>
+        <v>5.6338028169014086E-2</v>
       </c>
       <c r="H2">
         <f>AVL!$C$11</f>
-        <v>6.4935064935064929E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>5.6338028169014086E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>13</v>
       </c>
       <c r="B3">
         <f>AVL!$C$12</f>
-        <v>5.9523809523809521E-2</v>
+        <v>5.6338028169014086E-2</v>
       </c>
       <c r="C3">
         <f>AVL!$C$12</f>
-        <v>5.9523809523809521E-2</v>
+        <v>5.6338028169014086E-2</v>
       </c>
       <c r="D3">
         <f>AVL!$C$12</f>
-        <v>5.9523809523809521E-2</v>
+        <v>5.6338028169014086E-2</v>
       </c>
       <c r="E3">
         <f>AVL!$C$12</f>
-        <v>5.9523809523809521E-2</v>
+        <v>5.6338028169014086E-2</v>
       </c>
       <c r="F3">
         <f>AVL!$C$12</f>
-        <v>5.9523809523809521E-2</v>
+        <v>5.6338028169014086E-2</v>
       </c>
       <c r="G3">
         <f>AVL!$C$12</f>
-        <v>5.9523809523809521E-2</v>
+        <v>5.6338028169014086E-2</v>
       </c>
       <c r="H3">
         <f>AVL!$C$12</f>
-        <v>5.9523809523809521E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+        <v>5.6338028169014086E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1196,7 +1135,7 @@
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -1229,7 +1168,7 @@
         <v>2.9411764705882353E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1262,7 +1201,7 @@
         <v>3.0303030303030304E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -1296,26 +1235,12 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
     <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
@@ -1459,24 +1384,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30A502D4-C09A-449A-A258-EE541B816382}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{441C2D10-A603-4499-828F-5FADDAF9DE77}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1149AAAE-ABCC-460E-97F6-A6D332D4802A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1492,4 +1415,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30A502D4-C09A-449A-A258-EE541B816382}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{441C2D10-A603-4499-828F-5FADDAF9DE77}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/InputData/trans/SoCDTtiNTY/Share of Cargo Dist Transported that is New This Year.xlsx
+++ b/InputData/trans/SoCDTtiNTY/Share of Cargo Dist Transported that is New This Year.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-southkorea-ci\InputData\trans\SoCDTtiNTY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\SK\eps-southkorea\InputData\trans\SoCDTtiNTY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D1A8964-98DB-4AA4-BED4-2CA2BD5126D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E6DABE7-05FE-4BD2-AB7D-D541D2E0685D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38505" yWindow="-4650" windowWidth="19410" windowHeight="20985" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25260" yWindow="1515" windowWidth="24345" windowHeight="13980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -508,7 +508,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
@@ -577,9 +577,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DE974D0-35AB-448C-ABAC-291E7575B7A2}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="43.5">
+    <row r="1" spans="1:3" ht="45">
       <c r="A1" s="2" t="s">
         <v>26</v>
       </c>
@@ -595,7 +595,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="8">
-        <v>15.6</v>
+        <v>13</v>
       </c>
       <c r="C2" s="8">
         <v>17.75</v>
@@ -661,7 +661,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="43.5">
+    <row r="10" spans="1:3" ht="45">
       <c r="A10" s="2" t="s">
         <v>26</v>
       </c>
@@ -678,7 +678,7 @@
       </c>
       <c r="B11" s="7">
         <f>1/B2</f>
-        <v>6.4102564102564111E-2</v>
+        <v>7.6923076923076927E-2</v>
       </c>
       <c r="C11" s="7">
         <f>1/C2</f>
@@ -762,13 +762,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.08984375" customWidth="1"/>
-    <col min="2" max="8" width="14.453125" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" customWidth="1"/>
+    <col min="2" max="8" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="4" customFormat="1" ht="29">
+    <row r="1" spans="1:8" s="4" customFormat="1" ht="45">
       <c r="A1" s="2" t="s">
         <v>18</v>
       </c>
@@ -800,31 +800,31 @@
       </c>
       <c r="B2">
         <f>AVL!$B$11</f>
-        <v>6.4102564102564111E-2</v>
+        <v>7.6923076923076927E-2</v>
       </c>
       <c r="C2">
         <f>AVL!$B$11</f>
-        <v>6.4102564102564111E-2</v>
+        <v>7.6923076923076927E-2</v>
       </c>
       <c r="D2">
         <f>AVL!$B$11</f>
-        <v>6.4102564102564111E-2</v>
+        <v>7.6923076923076927E-2</v>
       </c>
       <c r="E2">
         <f>AVL!$B$11</f>
-        <v>6.4102564102564111E-2</v>
+        <v>7.6923076923076927E-2</v>
       </c>
       <c r="F2">
         <f>AVL!$B$11</f>
-        <v>6.4102564102564111E-2</v>
+        <v>7.6923076923076927E-2</v>
       </c>
       <c r="G2">
         <f>AVL!$B$11</f>
-        <v>6.4102564102564111E-2</v>
+        <v>7.6923076923076927E-2</v>
       </c>
       <c r="H2">
         <f>AVL!$B$11</f>
-        <v>6.4102564102564111E-2</v>
+        <v>7.6923076923076927E-2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1004,13 +1004,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.08984375" customWidth="1"/>
-    <col min="2" max="8" width="14.453125" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" customWidth="1"/>
+    <col min="2" max="8" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="4" customFormat="1" ht="29">
+    <row r="1" spans="1:8" s="4" customFormat="1" ht="45">
       <c r="A1" s="2" t="s">
         <v>18</v>
       </c>
@@ -1241,6 +1241,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
     <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
@@ -1384,12 +1390,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1400,6 +1400,15 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30A502D4-C09A-449A-A258-EE541B816382}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1149AAAE-ABCC-460E-97F6-A6D332D4802A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1417,15 +1426,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30A502D4-C09A-449A-A258-EE541B816382}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{441C2D10-A603-4499-828F-5FADDAF9DE77}">
   <ds:schemaRefs>

--- a/InputData/trans/SoCDTtiNTY/Share of Cargo Dist Transported that is New This Year.xlsx
+++ b/InputData/trans/SoCDTtiNTY/Share of Cargo Dist Transported that is New This Year.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\SK\eps-southkorea\InputData\trans\SoCDTtiNTY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\South Korea\Models\eps-southkorea\InputData\trans\SoCDTtiNTY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E6DABE7-05FE-4BD2-AB7D-D541D2E0685D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E18B893-E8CA-4EA1-96E1-8AA111939D2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25260" yWindow="1515" windowWidth="24345" windowHeight="13980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -799,32 +799,25 @@
         <v>12</v>
       </c>
       <c r="B2">
-        <f>AVL!$B$11</f>
-        <v>7.6923076923076927E-2</v>
+        <v>6.7000000000000004E-2</v>
       </c>
       <c r="C2">
-        <f>AVL!$B$11</f>
-        <v>7.6923076923076927E-2</v>
+        <v>6.7000000000000004E-2</v>
       </c>
       <c r="D2">
-        <f>AVL!$B$11</f>
-        <v>7.6923076923076927E-2</v>
+        <v>6.7000000000000004E-2</v>
       </c>
       <c r="E2">
-        <f>AVL!$B$11</f>
-        <v>7.6923076923076927E-2</v>
+        <v>6.7000000000000004E-2</v>
       </c>
       <c r="F2">
-        <f>AVL!$B$11</f>
-        <v>7.6923076923076927E-2</v>
+        <v>6.7000000000000004E-2</v>
       </c>
       <c r="G2">
-        <f>AVL!$B$11</f>
-        <v>7.6923076923076927E-2</v>
+        <v>6.7000000000000004E-2</v>
       </c>
       <c r="H2">
-        <f>AVL!$B$11</f>
-        <v>7.6923076923076927E-2</v>
+        <v>6.7000000000000004E-2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1241,9 +1234,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1391,19 +1387,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30A502D4-C09A-449A-A258-EE541B816382}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{441C2D10-A603-4499-828F-5FADDAF9DE77}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1427,9 +1419,10 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{441C2D10-A603-4499-828F-5FADDAF9DE77}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30A502D4-C09A-449A-A258-EE541B816382}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>